--- a/resources/ai-for-your-business/files/aifyb-adv-edge-selection.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-adv-edge-selection.xlsx
@@ -831,7 +831,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A longer fuse means NEXT quarter — deferred with a date, never binned.</t>
+          <t>A longer fuse means NEXT quarter — deferred with a date, never scrapped.</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="9">
-        <f>IF(LEFT(B9,7)&lt;&gt;"THROUGH","",IF(COUNTA(F9)=0,"no decision yet",IF(UPPER(TRIM(F9))="DEFER",IF(COUNTA(C9)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E9)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C9)*COUNTA(D9)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E9)),"CANNOT SELECT - the rough date must be a real date","selectable"))))))</f>
+        <f>IF(LEFT(B9,7)&lt;&gt;"THROUGH","",IF(COUNTA(F9)=0,"no decision yet",IF(UPPER(TRIM(F9))="DEFER",IF(COUNTA(C9)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E9)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C9)*COUNTA(D9)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E9)),"CANNOT SELECT - the rough date must be a real date","selectable")))))</f>
         <v/>
       </c>
     </row>
@@ -904,7 +904,7 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="9">
-        <f>IF(LEFT(B10,7)&lt;&gt;"THROUGH","",IF(COUNTA(F10)=0,"no decision yet",IF(UPPER(TRIM(F10))="DEFER",IF(COUNTA(C10)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E10)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C10)*COUNTA(D10)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E10)),"CANNOT SELECT - the rough date must be a real date","selectable"))))))</f>
+        <f>IF(LEFT(B10,7)&lt;&gt;"THROUGH","",IF(COUNTA(F10)=0,"no decision yet",IF(UPPER(TRIM(F10))="DEFER",IF(COUNTA(C10)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E10)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C10)*COUNTA(D10)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E10)),"CANNOT SELECT - the rough date must be a real date","selectable")))))</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="9">
-        <f>IF(LEFT(B11,7)&lt;&gt;"THROUGH","",IF(COUNTA(F11)=0,"no decision yet",IF(UPPER(TRIM(F11))="DEFER",IF(COUNTA(C11)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E11)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C11)*COUNTA(D11)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E11)),"CANNOT SELECT - the rough date must be a real date","selectable"))))))</f>
+        <f>IF(LEFT(B11,7)&lt;&gt;"THROUGH","",IF(COUNTA(F11)=0,"no decision yet",IF(UPPER(TRIM(F11))="DEFER",IF(COUNTA(C11)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E11)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C11)*COUNTA(D11)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E11)),"CANNOT SELECT - the rough date must be a real date","selectable")))))</f>
         <v/>
       </c>
     </row>
@@ -940,7 +940,7 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="9">
-        <f>IF(LEFT(B12,7)&lt;&gt;"THROUGH","",IF(COUNTA(F12)=0,"no decision yet",IF(UPPER(TRIM(F12))="DEFER",IF(COUNTA(C12)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E12)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C12)*COUNTA(D12)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E12)),"CANNOT SELECT - the rough date must be a real date","selectable"))))))</f>
+        <f>IF(LEFT(B12,7)&lt;&gt;"THROUGH","",IF(COUNTA(F12)=0,"no decision yet",IF(UPPER(TRIM(F12))="DEFER",IF(COUNTA(C12)=0,"DEFER - write the revival condition in the consequence column",IF(NOT(ISNUMBER(E12)),"DEFER - put a date on it, or it is an abandonment","deferred, with a reason")),IF(COUNTA(C12)*COUNTA(D12)=0,"CANNOT SELECT - needs a consequence and a route to client value",IF(NOT(ISNUMBER(E12)),"CANNOT SELECT - the rough date must be a real date","selectable")))))</f>
         <v/>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>If it did not materialise, we will record</t>
+          <t>If it did not materialize, we will record</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="B19" s="9">
-        <f>IF('Stage B - is it this quarter'!B18&lt;&gt;"OK - one selected, the rest deferred with reasons and dates","NOT COMPLETE - Stage B has not produced one valid selection yet",IF(COUNTA(B6:B17)&lt;12,"NOT COMPLETE - "&amp;(12-COUNTA(B6:B17))&amp;" field(s) still blank. An unsigned, undated baseline is not a baseline.",IF(NOT(ISNUMBER(B9)),"NOT COMPLETE - today's number must be a NUMBER",IF(OR(NOT(ISNUMBER(B10)),NOT(ISNUMBER(B14)),NOT(ISNUMBER(B15))),"NOT COMPLETE - the measured, accepted and go/no-go entries must be real DATES",IF(B15&lt;B10,"NOT COMPLETE - the go/no-go date cannot precede the measurement","COMPLETE - signed, dated, owner accepted"))))</f>
+        <f>IF('Stage B - is it this quarter'!B18&lt;&gt;"OK - one selected, the rest deferred with reasons and dates","NOT COMPLETE - Stage B has not produced one valid selection yet",IF(COUNTA(B6:B17)&lt;12,"NOT COMPLETE - "&amp;(12-COUNTA(B6:B17))&amp;" field(s) still blank. An unsigned, undated baseline is not a baseline.",IF(NOT(ISNUMBER(B9)),"NOT COMPLETE - today's number must be a NUMBER",IF(OR(NOT(ISNUMBER(B10)),NOT(ISNUMBER(B14)),NOT(ISNUMBER(B15))),"NOT COMPLETE - the measured, accepted and go/no-go entries must be real DATES",IF(B15&lt;B10,"NOT COMPLETE - the go/no-go date cannot precede the measurement","COMPLETE - signed, dated, owner accepted")))))</f>
         <v/>
       </c>
     </row>

--- a/resources/ai-for-your-business/files/aifyb-adv-edge-selection.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-adv-edge-selection.xlsx
@@ -740,7 +740,7 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
